--- a/operations/Audacion_AI_Labs_Full_Budget.xlsx
+++ b/operations/Audacion_AI_Labs_Full_Budget.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Nonprofit Personnel" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="PBC Revenue" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Nonprofit Revenue" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Summary" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="PBC Summary" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Nonprofit Summary" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="193">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -534,6 +535,12 @@
     <t xml:space="preserve">TOTAL NONPROFIT REVENUE</t>
   </si>
   <si>
+    <t xml:space="preserve">AUDACION AI LABS PBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial Summary</t>
+  </si>
+  <si>
     <t xml:space="preserve">Low</t>
   </si>
   <si>
@@ -546,37 +553,58 @@
     <t xml:space="preserve">EXPENSES</t>
   </si>
   <si>
-    <t xml:space="preserve">PBC Personnel (fully loaded)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PBC Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nonprofit Personnel (fully loaded)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL EXPENSES</t>
+    <t xml:space="preserve">Personnel (44 roles, fully loaded at 25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL PBC EXPENSES</t>
   </si>
   <si>
     <t xml:space="preserve">REVENUE</t>
   </si>
   <si>
-    <t xml:space="preserve">PBC Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nonprofit Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL REVENUE</t>
+    <t xml:space="preserve">PBC Earned Revenue (16 streams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PBC Grants (SBIR, State, Corporate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract Revenue from Nonprofit (grant-funded research)</t>
   </si>
   <si>
     <t xml:space="preserve">NET (Revenue minus Expenses)</t>
   </si>
   <si>
-    <t xml:space="preserve">ANNUAL TARGET</t>
+    <t xml:space="preserve">PBC ANNUAL REVENUE TARGET</t>
   </si>
   <si>
     <t xml:space="preserve">GAP TO TARGET (from mid revenue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRISM RESEARCH INSTITUTE 501(c)(3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnel (3 roles, fully loaded at 25%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nonprofit Operations (admin, filing, insurance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contract Payments to PBC (grant-funded research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL NONPROFIT EXPENSES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTE: Net surplus funds research contracts to the PBC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The "Contract Payments to PBC" expense line = the PBC "Contract Revenue from Nonprofit" line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When you set one, update the other to match.</t>
   </si>
 </sst>
 </file>
@@ -588,7 +616,7 @@
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,6 +665,51 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1A1A2E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF339933"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -717,8 +790,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -726,43 +803,67 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -794,7 +895,7 @@
       <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFCC3333"/>
+      <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFE8E8F0"/>
       <rgbColor rgb="FF660066"/>
@@ -823,7 +924,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFCC9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF666666"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339933"/>
@@ -1022,2453 +1123,2453 @@
   <dimension ref="A1:N57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <f aca="false">AVERAGE(F3,G3)</f>
         <v>250000</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="6" t="n">
         <f aca="false">H3*I3</f>
         <v>62500</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="6" t="n">
         <f aca="false">H3+J3</f>
         <v>312500</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="6" t="n">
         <f aca="false">F3*C3</f>
         <v>200000</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="6" t="n">
         <f aca="false">G3*C3</f>
         <v>300000</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="6" t="n">
         <f aca="false">K3*C3</f>
         <v>312500</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>250000</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>350000</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <f aca="false">AVERAGE(F4,G4)</f>
         <v>300000</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <f aca="false">H4*I4</f>
         <v>75000</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <f aca="false">H4+J4</f>
         <v>375000</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="6" t="n">
         <f aca="false">F4*C4</f>
         <v>250000</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="6" t="n">
         <f aca="false">G4*C4</f>
         <v>350000</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="6" t="n">
         <f aca="false">K4*C4</f>
         <v>375000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <f aca="false">AVERAGE(F5,G5)</f>
         <v>175000</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <f aca="false">H5*I5</f>
         <v>43750</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="6" t="n">
         <f aca="false">H5+J5</f>
         <v>218750</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="6" t="n">
         <f aca="false">F5*C5</f>
         <v>150000</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="6" t="n">
         <f aca="false">G5*C5</f>
         <v>200000</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="6" t="n">
         <f aca="false">K5*C5</f>
         <v>218750</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>220000</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <f aca="false">AVERAGE(F7,G7)</f>
         <v>260000</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <f aca="false">H7*I7</f>
         <v>65000</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <f aca="false">H7+J7</f>
         <v>325000</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" s="6" t="n">
         <f aca="false">F7*C7</f>
         <v>220000</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="6" t="n">
         <f aca="false">G7*C7</f>
         <v>300000</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="6" t="n">
         <f aca="false">K7*C7</f>
         <v>325000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>170000</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>230000</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="6" t="n">
         <f aca="false">AVERAGE(F8,G8)</f>
         <v>200000</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <f aca="false">H8*I8</f>
         <v>50000</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K8" s="6" t="n">
         <f aca="false">H8+J8</f>
         <v>250000</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" s="6" t="n">
         <f aca="false">F8*C8</f>
         <v>170000</v>
       </c>
-      <c r="M8" s="5" t="n">
+      <c r="M8" s="6" t="n">
         <f aca="false">G8*C8</f>
         <v>230000</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="N8" s="6" t="n">
         <f aca="false">K8*C8</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>170000</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="5" t="n">
         <v>230000</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <f aca="false">AVERAGE(F9,G9)</f>
         <v>200000</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <f aca="false">H9*I9</f>
         <v>50000</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="6" t="n">
         <f aca="false">H9+J9</f>
         <v>250000</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="6" t="n">
         <f aca="false">F9*C9</f>
         <v>170000</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M9" s="6" t="n">
         <f aca="false">G9*C9</f>
         <v>230000</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="N9" s="6" t="n">
         <f aca="false">K9*C9</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>170000</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="5" t="n">
         <v>230000</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="6" t="n">
         <f aca="false">AVERAGE(F10,G10)</f>
         <v>200000</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <f aca="false">H10*I10</f>
         <v>50000</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K10" s="6" t="n">
         <f aca="false">H10+J10</f>
         <v>250000</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L10" s="6" t="n">
         <f aca="false">F10*C10</f>
         <v>170000</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M10" s="6" t="n">
         <f aca="false">G10*C10</f>
         <v>230000</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="N10" s="6" t="n">
         <f aca="false">K10*C10</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>170000</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>230000</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="6" t="n">
         <f aca="false">AVERAGE(F11,G11)</f>
         <v>200000</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="6" t="n">
         <f aca="false">H11*I11</f>
         <v>50000</v>
       </c>
-      <c r="K11" s="5" t="n">
+      <c r="K11" s="6" t="n">
         <f aca="false">H11+J11</f>
         <v>250000</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="L11" s="6" t="n">
         <f aca="false">F11*C11</f>
         <v>170000</v>
       </c>
-      <c r="M11" s="5" t="n">
+      <c r="M11" s="6" t="n">
         <f aca="false">G11*C11</f>
         <v>230000</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="N11" s="6" t="n">
         <f aca="false">K11*C11</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>170000</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="5" t="n">
         <v>230000</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="6" t="n">
         <f aca="false">AVERAGE(F12,G12)</f>
         <v>200000</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="6" t="n">
         <f aca="false">H12*I12</f>
         <v>50000</v>
       </c>
-      <c r="K12" s="5" t="n">
+      <c r="K12" s="6" t="n">
         <f aca="false">H12+J12</f>
         <v>250000</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="L12" s="6" t="n">
         <f aca="false">F12*C12</f>
         <v>170000</v>
       </c>
-      <c r="M12" s="5" t="n">
+      <c r="M12" s="6" t="n">
         <f aca="false">G12*C12</f>
         <v>230000</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="N12" s="6" t="n">
         <f aca="false">K12*C12</f>
         <v>250000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>95000</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>135000</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="6" t="n">
         <f aca="false">AVERAGE(F13,G13)</f>
         <v>115000</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="6" t="n">
         <f aca="false">H13*I13</f>
         <v>28750</v>
       </c>
-      <c r="K13" s="5" t="n">
+      <c r="K13" s="6" t="n">
         <f aca="false">H13+J13</f>
         <v>143750</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L13" s="6" t="n">
         <f aca="false">F13*C13</f>
         <v>95000</v>
       </c>
-      <c r="M13" s="5" t="n">
+      <c r="M13" s="6" t="n">
         <f aca="false">G13*C13</f>
         <v>135000</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="N13" s="6" t="n">
         <f aca="false">K13*C13</f>
         <v>143750</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>95000</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>135000</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="6" t="n">
         <f aca="false">AVERAGE(F14,G14)</f>
         <v>115000</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J14" s="6" t="n">
         <f aca="false">H14*I14</f>
         <v>28750</v>
       </c>
-      <c r="K14" s="5" t="n">
+      <c r="K14" s="6" t="n">
         <f aca="false">H14+J14</f>
         <v>143750</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="L14" s="6" t="n">
         <f aca="false">F14*C14</f>
         <v>95000</v>
       </c>
-      <c r="M14" s="5" t="n">
+      <c r="M14" s="6" t="n">
         <f aca="false">G14*C14</f>
         <v>135000</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="N14" s="6" t="n">
         <f aca="false">K14*C14</f>
         <v>143750</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>95000</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>135000</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="6" t="n">
         <f aca="false">AVERAGE(F15,G15)</f>
         <v>115000</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J15" s="6" t="n">
         <f aca="false">H15*I15</f>
         <v>28750</v>
       </c>
-      <c r="K15" s="5" t="n">
+      <c r="K15" s="6" t="n">
         <f aca="false">H15+J15</f>
         <v>143750</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="L15" s="6" t="n">
         <f aca="false">F15*C15</f>
         <v>95000</v>
       </c>
-      <c r="M15" s="5" t="n">
+      <c r="M15" s="6" t="n">
         <f aca="false">G15*C15</f>
         <v>135000</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="N15" s="6" t="n">
         <f aca="false">K15*C15</f>
         <v>143750</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>120000</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>160000</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="6" t="n">
         <f aca="false">AVERAGE(F16,G16)</f>
         <v>140000</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J16" s="6" t="n">
         <f aca="false">H16*I16</f>
         <v>35000</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="K16" s="6" t="n">
         <f aca="false">H16+J16</f>
         <v>175000</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L16" s="6" t="n">
         <f aca="false">F16*C16</f>
         <v>120000</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="M16" s="6" t="n">
         <f aca="false">G16*C16</f>
         <v>160000</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="N16" s="6" t="n">
         <f aca="false">K16*C16</f>
         <v>175000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>85000</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>120000</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="6" t="n">
         <f aca="false">AVERAGE(F17,G17)</f>
         <v>102500</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J17" s="6" t="n">
         <f aca="false">H17*I17</f>
         <v>25625</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="K17" s="6" t="n">
         <f aca="false">H17+J17</f>
         <v>128125</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="L17" s="6" t="n">
         <f aca="false">F17*C17</f>
         <v>85000</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="M17" s="6" t="n">
         <f aca="false">G17*C17</f>
         <v>120000</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="N17" s="6" t="n">
         <f aca="false">K17*C17</f>
         <v>128125</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="5" t="n">
         <v>40000</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="5" t="n">
         <v>60000</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="6" t="n">
         <f aca="false">AVERAGE(F18,G18)</f>
         <v>50000</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J18" s="6" t="n">
         <f aca="false">H18*I18</f>
         <v>12500</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="K18" s="6" t="n">
         <f aca="false">H18+J18</f>
         <v>62500</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="L18" s="6" t="n">
         <f aca="false">F18*C18</f>
         <v>40000</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="M18" s="6" t="n">
         <f aca="false">G18*C18</f>
         <v>60000</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="N18" s="6" t="n">
         <f aca="false">K18*C18</f>
         <v>62500</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>160000</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>220000</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="6" t="n">
         <f aca="false">AVERAGE(F19,G19)</f>
         <v>190000</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J19" s="6" t="n">
         <f aca="false">H19*I19</f>
         <v>47500</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="K19" s="6" t="n">
         <f aca="false">H19+J19</f>
         <v>237500</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="L19" s="6" t="n">
         <f aca="false">F19*C19</f>
         <v>160000</v>
       </c>
-      <c r="M19" s="5" t="n">
+      <c r="M19" s="6" t="n">
         <f aca="false">G19*C19</f>
         <v>220000</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="N19" s="6" t="n">
         <f aca="false">K19*C19</f>
         <v>237500</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>30000</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" s="6" t="n">
         <f aca="false">AVERAGE(F20,G20)</f>
         <v>40000</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J20" s="6" t="n">
         <f aca="false">H20*I20</f>
         <v>10000</v>
       </c>
-      <c r="K20" s="5" t="n">
+      <c r="K20" s="6" t="n">
         <f aca="false">H20+J20</f>
         <v>50000</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="L20" s="6" t="n">
         <f aca="false">F20*C20</f>
         <v>30000</v>
       </c>
-      <c r="M20" s="5" t="n">
+      <c r="M20" s="6" t="n">
         <f aca="false">G20*C20</f>
         <v>50000</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="N20" s="6" t="n">
         <f aca="false">K20*C20</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="5" t="n">
         <v>275000</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="6" t="n">
         <f aca="false">AVERAGE(F22,G22)</f>
         <v>237500</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="6" t="n">
         <f aca="false">H22*I22</f>
         <v>59375</v>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="K22" s="6" t="n">
         <f aca="false">H22+J22</f>
         <v>296875</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="L22" s="6" t="n">
         <f aca="false">F22*C22</f>
         <v>200000</v>
       </c>
-      <c r="M22" s="5" t="n">
+      <c r="M22" s="6" t="n">
         <f aca="false">G22*C22</f>
         <v>275000</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="N22" s="6" t="n">
         <f aca="false">K22*C22</f>
         <v>296875</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>155000</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="5" t="n">
         <v>210000</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="6" t="n">
         <f aca="false">AVERAGE(F23,G23)</f>
         <v>182500</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="6" t="n">
         <f aca="false">H23*I23</f>
         <v>45625</v>
       </c>
-      <c r="K23" s="5" t="n">
+      <c r="K23" s="6" t="n">
         <f aca="false">H23+J23</f>
         <v>228125</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="L23" s="6" t="n">
         <f aca="false">F23*C23</f>
         <v>155000</v>
       </c>
-      <c r="M23" s="5" t="n">
+      <c r="M23" s="6" t="n">
         <f aca="false">G23*C23</f>
         <v>210000</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="N23" s="6" t="n">
         <f aca="false">K23*C23</f>
         <v>228125</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>45000</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="5" t="n">
         <v>65000</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="6" t="n">
         <f aca="false">AVERAGE(F24,G24)</f>
         <v>55000</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="6" t="n">
         <f aca="false">H24*I24</f>
         <v>13750</v>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="K24" s="6" t="n">
         <f aca="false">H24+J24</f>
         <v>68750</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L24" s="6" t="n">
         <f aca="false">F24*C24</f>
         <v>45000</v>
       </c>
-      <c r="M24" s="5" t="n">
+      <c r="M24" s="6" t="n">
         <f aca="false">G24*C24</f>
         <v>65000</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="N24" s="6" t="n">
         <f aca="false">K24*C24</f>
         <v>68750</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>160000</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="5" t="n">
         <v>220000</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="6" t="n">
         <f aca="false">AVERAGE(F25,G25)</f>
         <v>190000</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="6" t="n">
         <f aca="false">H25*I25</f>
         <v>47500</v>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="K25" s="6" t="n">
         <f aca="false">H25+J25</f>
         <v>237500</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" s="6" t="n">
         <f aca="false">F25*C25</f>
         <v>160000</v>
       </c>
-      <c r="M25" s="5" t="n">
+      <c r="M25" s="6" t="n">
         <f aca="false">G25*C25</f>
         <v>220000</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="N25" s="6" t="n">
         <f aca="false">K25*C25</f>
         <v>237500</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="6" t="n">
         <f aca="false">AVERAGE(F27,G27)</f>
         <v>175000</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="6" t="n">
         <f aca="false">H27*I27</f>
         <v>43750</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="K27" s="6" t="n">
         <f aca="false">H27+J27</f>
         <v>218750</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L27" s="6" t="n">
         <f aca="false">F27*C27</f>
         <v>150000</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="M27" s="6" t="n">
         <f aca="false">G27*C27</f>
         <v>200000</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="N27" s="6" t="n">
         <f aca="false">K27*C27</f>
         <v>218750</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="5" t="n">
         <v>140000</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="6" t="n">
         <f aca="false">AVERAGE(F28,G28)</f>
         <v>120000</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="J28" s="6" t="n">
         <f aca="false">H28*I28</f>
         <v>30000</v>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="K28" s="6" t="n">
         <f aca="false">H28+J28</f>
         <v>150000</v>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="L28" s="6" t="n">
         <f aca="false">F28*C28</f>
         <v>100000</v>
       </c>
-      <c r="M28" s="5" t="n">
+      <c r="M28" s="6" t="n">
         <f aca="false">G28*C28</f>
         <v>140000</v>
       </c>
-      <c r="N28" s="5" t="n">
+      <c r="N28" s="6" t="n">
         <f aca="false">K28*C28</f>
         <v>150000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="6" t="n">
         <f aca="false">AVERAGE(F29,G29)</f>
         <v>175000</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="6" t="n">
         <f aca="false">H29*I29</f>
         <v>43750</v>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="K29" s="6" t="n">
         <f aca="false">H29+J29</f>
         <v>218750</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L29" s="6" t="n">
         <f aca="false">F29*C29</f>
         <v>150000</v>
       </c>
-      <c r="M29" s="5" t="n">
+      <c r="M29" s="6" t="n">
         <f aca="false">G29*C29</f>
         <v>200000</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="N29" s="6" t="n">
         <f aca="false">K29*C29</f>
         <v>218750</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>140000</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="5" t="n">
         <v>180000</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="6" t="n">
         <f aca="false">AVERAGE(F30,G30)</f>
         <v>160000</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J30" s="6" t="n">
         <f aca="false">H30*I30</f>
         <v>40000</v>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="K30" s="6" t="n">
         <f aca="false">H30+J30</f>
         <v>200000</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="L30" s="6" t="n">
         <f aca="false">F30*C30</f>
         <v>140000</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="M30" s="6" t="n">
         <f aca="false">G30*C30</f>
         <v>180000</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="N30" s="6" t="n">
         <f aca="false">K30*C30</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="C32" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="6" t="n">
         <f aca="false">AVERAGE(F32,G32)</f>
         <v>130000</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J32" s="6" t="n">
         <f aca="false">H32*I32</f>
         <v>32500</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="K32" s="6" t="n">
         <f aca="false">H32+J32</f>
         <v>162500</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="L32" s="6" t="n">
         <f aca="false">F32*C32</f>
         <v>110000</v>
       </c>
-      <c r="M32" s="5" t="n">
+      <c r="M32" s="6" t="n">
         <f aca="false">G32*C32</f>
         <v>150000</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="N32" s="6" t="n">
         <f aca="false">K32*C32</f>
         <v>162500</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="C33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="5" t="n">
         <v>65000</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="5" t="n">
         <v>90000</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="6" t="n">
         <f aca="false">AVERAGE(F33,G33)</f>
         <v>77500</v>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I33" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J33" s="6" t="n">
         <f aca="false">H33*I33</f>
         <v>19375</v>
       </c>
-      <c r="K33" s="5" t="n">
+      <c r="K33" s="6" t="n">
         <f aca="false">H33+J33</f>
         <v>96875</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="L33" s="6" t="n">
         <f aca="false">F33*C33</f>
         <v>65000</v>
       </c>
-      <c r="M33" s="5" t="n">
+      <c r="M33" s="6" t="n">
         <f aca="false">G33*C33</f>
         <v>90000</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="N33" s="6" t="n">
         <f aca="false">K33*C33</f>
         <v>96875</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="5" t="n">
         <v>130000</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="5" t="n">
         <v>175000</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H35" s="6" t="n">
         <f aca="false">AVERAGE(F35,G35)</f>
         <v>152500</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J35" s="6" t="n">
         <f aca="false">H35*I35</f>
         <v>38125</v>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="K35" s="6" t="n">
         <f aca="false">H35+J35</f>
         <v>190625</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="L35" s="6" t="n">
         <f aca="false">F35*C35</f>
         <v>130000</v>
       </c>
-      <c r="M35" s="5" t="n">
+      <c r="M35" s="6" t="n">
         <f aca="false">G35*C35</f>
         <v>175000</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="N35" s="6" t="n">
         <f aca="false">K35*C35</f>
         <v>190625</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="C36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" s="6" t="n">
         <f aca="false">AVERAGE(F36,G36)</f>
         <v>130000</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="J36" s="6" t="n">
         <f aca="false">H36*I36</f>
         <v>32500</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="K36" s="6" t="n">
         <f aca="false">H36+J36</f>
         <v>162500</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="L36" s="6" t="n">
         <f aca="false">F36*C36</f>
         <v>110000</v>
       </c>
-      <c r="M36" s="5" t="n">
+      <c r="M36" s="6" t="n">
         <f aca="false">G36*C36</f>
         <v>150000</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="N36" s="6" t="n">
         <f aca="false">K36*C36</f>
         <v>162500</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="5" t="n">
         <v>95000</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="5" t="n">
         <v>135000</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="6" t="n">
         <f aca="false">AVERAGE(F37,G37)</f>
         <v>115000</v>
       </c>
-      <c r="I37" s="6" t="n">
+      <c r="I37" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="J37" s="6" t="n">
         <f aca="false">H37*I37</f>
         <v>28750</v>
       </c>
-      <c r="K37" s="5" t="n">
+      <c r="K37" s="6" t="n">
         <f aca="false">H37+J37</f>
         <v>143750</v>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="L37" s="6" t="n">
         <f aca="false">F37*C37</f>
         <v>95000</v>
       </c>
-      <c r="M37" s="5" t="n">
+      <c r="M37" s="6" t="n">
         <f aca="false">G37*C37</f>
         <v>135000</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="N37" s="6" t="n">
         <f aca="false">K37*C37</f>
         <v>143750</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="5" t="n">
         <v>115000</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="5" t="n">
         <v>155000</v>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" s="6" t="n">
         <f aca="false">AVERAGE(F38,G38)</f>
         <v>135000</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="J38" s="6" t="n">
         <f aca="false">H38*I38</f>
         <v>33750</v>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="K38" s="6" t="n">
         <f aca="false">H38+J38</f>
         <v>168750</v>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="L38" s="6" t="n">
         <f aca="false">F38*C38</f>
         <v>115000</v>
       </c>
-      <c r="M38" s="5" t="n">
+      <c r="M38" s="6" t="n">
         <f aca="false">G38*C38</f>
         <v>155000</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="N38" s="6" t="n">
         <f aca="false">K38*C38</f>
         <v>168750</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="5" t="n">
         <v>90000</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="5" t="n">
         <v>130000</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39" s="6" t="n">
         <f aca="false">AVERAGE(F39,G39)</f>
         <v>110000</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="J39" s="6" t="n">
         <f aca="false">H39*I39</f>
         <v>27500</v>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="K39" s="6" t="n">
         <f aca="false">H39+J39</f>
         <v>137500</v>
       </c>
-      <c r="L39" s="5" t="n">
+      <c r="L39" s="6" t="n">
         <f aca="false">F39*C39</f>
         <v>90000</v>
       </c>
-      <c r="M39" s="5" t="n">
+      <c r="M39" s="6" t="n">
         <f aca="false">G39*C39</f>
         <v>130000</v>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="N39" s="6" t="n">
         <f aca="false">K39*C39</f>
         <v>137500</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="5" t="n">
         <v>140000</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="5" t="n">
         <v>185000</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="6" t="n">
         <f aca="false">AVERAGE(F41,G41)</f>
         <v>162500</v>
       </c>
-      <c r="I41" s="6" t="n">
+      <c r="I41" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J41" s="5" t="n">
+      <c r="J41" s="6" t="n">
         <f aca="false">H41*I41</f>
         <v>40625</v>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="K41" s="6" t="n">
         <f aca="false">H41+J41</f>
         <v>203125</v>
       </c>
-      <c r="L41" s="5" t="n">
+      <c r="L41" s="6" t="n">
         <f aca="false">F41*C41</f>
         <v>140000</v>
       </c>
-      <c r="M41" s="5" t="n">
+      <c r="M41" s="6" t="n">
         <f aca="false">G41*C41</f>
         <v>185000</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="N41" s="6" t="n">
         <f aca="false">K41*C41</f>
         <v>203125</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="C42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="5" t="n">
         <v>75000</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="6" t="n">
         <f aca="false">AVERAGE(F42,G42)</f>
         <v>92500</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="J42" s="6" t="n">
         <f aca="false">H42*I42</f>
         <v>23125</v>
       </c>
-      <c r="K42" s="5" t="n">
+      <c r="K42" s="6" t="n">
         <f aca="false">H42+J42</f>
         <v>115625</v>
       </c>
-      <c r="L42" s="5" t="n">
+      <c r="L42" s="6" t="n">
         <f aca="false">F42*C42</f>
         <v>75000</v>
       </c>
-      <c r="M42" s="5" t="n">
+      <c r="M42" s="6" t="n">
         <f aca="false">G42*C42</f>
         <v>110000</v>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="N42" s="6" t="n">
         <f aca="false">K42*C42</f>
         <v>115625</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="n">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="C44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="6" t="n">
         <f aca="false">AVERAGE(F44,G44)</f>
         <v>130000</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="J44" s="6" t="n">
         <f aca="false">H44*I44</f>
         <v>32500</v>
       </c>
-      <c r="K44" s="5" t="n">
+      <c r="K44" s="6" t="n">
         <f aca="false">H44+J44</f>
         <v>162500</v>
       </c>
-      <c r="L44" s="5" t="n">
+      <c r="L44" s="6" t="n">
         <f aca="false">F44*C44</f>
         <v>110000</v>
       </c>
-      <c r="M44" s="5" t="n">
+      <c r="M44" s="6" t="n">
         <f aca="false">G44*C44</f>
         <v>150000</v>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="N44" s="6" t="n">
         <f aca="false">K44*C44</f>
         <v>162500</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="C46" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="H46" s="5" t="n">
+      <c r="H46" s="6" t="n">
         <f aca="false">AVERAGE(F46,G46)</f>
         <v>130000</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J46" s="5" t="n">
+      <c r="J46" s="6" t="n">
         <f aca="false">H46*I46</f>
         <v>32500</v>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="K46" s="6" t="n">
         <f aca="false">H46+J46</f>
         <v>162500</v>
       </c>
-      <c r="L46" s="5" t="n">
+      <c r="L46" s="6" t="n">
         <f aca="false">F46*C46</f>
         <v>110000</v>
       </c>
-      <c r="M46" s="5" t="n">
+      <c r="M46" s="6" t="n">
         <f aca="false">G46*C46</f>
         <v>150000</v>
       </c>
-      <c r="N46" s="5" t="n">
+      <c r="N46" s="6" t="n">
         <f aca="false">K46*C46</f>
         <v>162500</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="C47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F47" s="5" t="n">
         <v>125000</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="5" t="n">
         <v>170000</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="H47" s="6" t="n">
         <f aca="false">AVERAGE(F47,G47)</f>
         <v>147500</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J47" s="5" t="n">
+      <c r="J47" s="6" t="n">
         <f aca="false">H47*I47</f>
         <v>36875</v>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="K47" s="6" t="n">
         <f aca="false">H47+J47</f>
         <v>184375</v>
       </c>
-      <c r="L47" s="5" t="n">
+      <c r="L47" s="6" t="n">
         <f aca="false">F47*C47</f>
         <v>125000</v>
       </c>
-      <c r="M47" s="5" t="n">
+      <c r="M47" s="6" t="n">
         <f aca="false">G47*C47</f>
         <v>170000</v>
       </c>
-      <c r="N47" s="5" t="n">
+      <c r="N47" s="6" t="n">
         <f aca="false">K47*C47</f>
         <v>184375</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="C48" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="5" t="n">
         <v>26000</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="5" t="n">
         <v>36000</v>
       </c>
-      <c r="H48" s="5" t="n">
+      <c r="H48" s="6" t="n">
         <f aca="false">AVERAGE(F48,G48)</f>
         <v>31000</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J48" s="5" t="n">
+      <c r="J48" s="6" t="n">
         <f aca="false">H48*I48</f>
         <v>7750</v>
       </c>
-      <c r="K48" s="5" t="n">
+      <c r="K48" s="6" t="n">
         <f aca="false">H48+J48</f>
         <v>38750</v>
       </c>
-      <c r="L48" s="5" t="n">
+      <c r="L48" s="6" t="n">
         <f aca="false">F48*C48</f>
         <v>26000</v>
       </c>
-      <c r="M48" s="5" t="n">
+      <c r="M48" s="6" t="n">
         <f aca="false">G48*C48</f>
         <v>36000</v>
       </c>
-      <c r="N48" s="5" t="n">
+      <c r="N48" s="6" t="n">
         <f aca="false">K48*C48</f>
         <v>38750</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="C49" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F49" s="5" t="n">
         <v>55000</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="5" t="n">
         <v>75000</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="6" t="n">
         <f aca="false">AVERAGE(F49,G49)</f>
         <v>65000</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J49" s="5" t="n">
+      <c r="J49" s="6" t="n">
         <f aca="false">H49*I49</f>
         <v>16250</v>
       </c>
-      <c r="K49" s="5" t="n">
+      <c r="K49" s="6" t="n">
         <f aca="false">H49+J49</f>
         <v>81250</v>
       </c>
-      <c r="L49" s="5" t="n">
+      <c r="L49" s="6" t="n">
         <f aca="false">F49*C49</f>
         <v>55000</v>
       </c>
-      <c r="M49" s="5" t="n">
+      <c r="M49" s="6" t="n">
         <f aca="false">G49*C49</f>
         <v>75000</v>
       </c>
-      <c r="N49" s="5" t="n">
+      <c r="N49" s="6" t="n">
         <f aca="false">K49*C49</f>
         <v>81250</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="C50" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="H50" s="5" t="n">
+      <c r="H50" s="6" t="n">
         <f aca="false">AVERAGE(F50,G50)</f>
         <v>130000</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J50" s="5" t="n">
+      <c r="J50" s="6" t="n">
         <f aca="false">H50*I50</f>
         <v>32500</v>
       </c>
-      <c r="K50" s="5" t="n">
+      <c r="K50" s="6" t="n">
         <f aca="false">H50+J50</f>
         <v>162500</v>
       </c>
-      <c r="L50" s="5" t="n">
+      <c r="L50" s="6" t="n">
         <f aca="false">F50*C50</f>
         <v>110000</v>
       </c>
-      <c r="M50" s="5" t="n">
+      <c r="M50" s="6" t="n">
         <f aca="false">G50*C50</f>
         <v>150000</v>
       </c>
-      <c r="N50" s="5" t="n">
+      <c r="N50" s="6" t="n">
         <f aca="false">K50*C50</f>
         <v>162500</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="C51" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="F51" s="5" t="n">
         <v>95000</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="5" t="n">
         <v>135000</v>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H51" s="6" t="n">
         <f aca="false">AVERAGE(F51,G51)</f>
         <v>115000</v>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I51" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J51" s="5" t="n">
+      <c r="J51" s="6" t="n">
         <f aca="false">H51*I51</f>
         <v>28750</v>
       </c>
-      <c r="K51" s="5" t="n">
+      <c r="K51" s="6" t="n">
         <f aca="false">H51+J51</f>
         <v>143750</v>
       </c>
-      <c r="L51" s="5" t="n">
+      <c r="L51" s="6" t="n">
         <f aca="false">F51*C51</f>
         <v>95000</v>
       </c>
-      <c r="M51" s="5" t="n">
+      <c r="M51" s="6" t="n">
         <f aca="false">G51*C51</f>
         <v>135000</v>
       </c>
-      <c r="N51" s="5" t="n">
+      <c r="N51" s="6" t="n">
         <f aca="false">K51*C51</f>
         <v>143750</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="C52" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F52" s="5" t="n">
         <v>75000</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="H52" s="6" t="n">
         <f aca="false">AVERAGE(F52,G52)</f>
         <v>92500</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I52" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J52" s="5" t="n">
+      <c r="J52" s="6" t="n">
         <f aca="false">H52*I52</f>
         <v>23125</v>
       </c>
-      <c r="K52" s="5" t="n">
+      <c r="K52" s="6" t="n">
         <f aca="false">H52+J52</f>
         <v>115625</v>
       </c>
-      <c r="L52" s="5" t="n">
+      <c r="L52" s="6" t="n">
         <f aca="false">F52*C52</f>
         <v>75000</v>
       </c>
-      <c r="M52" s="5" t="n">
+      <c r="M52" s="6" t="n">
         <f aca="false">G52*C52</f>
         <v>110000</v>
       </c>
-      <c r="N52" s="5" t="n">
+      <c r="N52" s="6" t="n">
         <f aca="false">K52*C52</f>
         <v>115625</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="C53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="F53" s="5" t="n">
         <v>36000</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="5" t="n">
         <v>72000</v>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H53" s="6" t="n">
         <f aca="false">AVERAGE(F53,G53)</f>
         <v>54000</v>
       </c>
-      <c r="I53" s="6" t="n">
+      <c r="I53" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J53" s="5" t="n">
+      <c r="J53" s="6" t="n">
         <f aca="false">H53*I53</f>
         <v>13500</v>
       </c>
-      <c r="K53" s="5" t="n">
+      <c r="K53" s="6" t="n">
         <f aca="false">H53+J53</f>
         <v>67500</v>
       </c>
-      <c r="L53" s="5" t="n">
+      <c r="L53" s="6" t="n">
         <f aca="false">F53*C53</f>
         <v>36000</v>
       </c>
-      <c r="M53" s="5" t="n">
+      <c r="M53" s="6" t="n">
         <f aca="false">G53*C53</f>
         <v>72000</v>
       </c>
-      <c r="N53" s="5" t="n">
+      <c r="N53" s="6" t="n">
         <f aca="false">K53*C53</f>
         <v>67500</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3"/>
+      <c r="B54" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="n">
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="C55" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="5" t="n">
         <v>95000</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="5" t="n">
         <v>140000</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H55" s="6" t="n">
         <f aca="false">AVERAGE(F55,G55)</f>
         <v>117500</v>
       </c>
-      <c r="I55" s="6" t="n">
+      <c r="I55" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J55" s="5" t="n">
+      <c r="J55" s="6" t="n">
         <f aca="false">H55*I55</f>
         <v>29375</v>
       </c>
-      <c r="K55" s="5" t="n">
+      <c r="K55" s="6" t="n">
         <f aca="false">H55+J55</f>
         <v>146875</v>
       </c>
-      <c r="L55" s="5" t="n">
+      <c r="L55" s="6" t="n">
         <f aca="false">F55*C55</f>
         <v>95000</v>
       </c>
-      <c r="M55" s="5" t="n">
+      <c r="M55" s="6" t="n">
         <f aca="false">G55*C55</f>
         <v>140000</v>
       </c>
-      <c r="N55" s="5" t="n">
+      <c r="N55" s="6" t="n">
         <f aca="false">K55*C55</f>
         <v>146875</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="7" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="L57" s="8" t="n">
+      <c r="L57" s="9" t="n">
         <f aca="false">SUM(L2:L55)</f>
         <v>5257000</v>
       </c>
-      <c r="M57" s="8" t="n">
+      <c r="M57" s="9" t="n">
         <f aca="false">SUM(M2:M55)</f>
         <v>7273000</v>
       </c>
-      <c r="N57" s="8" t="n">
+      <c r="N57" s="9" t="n">
         <f aca="false">SUM(N2:N55)</f>
         <v>7831250</v>
       </c>
@@ -3493,203 +3594,203 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>600000</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <f aca="false">AVERAGE(B2,C2)</f>
         <v>450000</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>400000</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <f aca="false">AVERAGE(B3,C3)</f>
         <v>300000</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>1500000</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <f aca="false">AVERAGE(B4,C4)</f>
         <v>1000000</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>400000</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <f aca="false">AVERAGE(B5,C5)</f>
         <v>300000</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>400000</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <f aca="false">AVERAGE(B6,C6)</f>
         <v>300000</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <f aca="false">AVERAGE(B7,C7)</f>
         <v>225000</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <f aca="false">AVERAGE(B8,C8)</f>
         <v>150000</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <f aca="false">AVERAGE(B9,C9)</f>
         <v>150000</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <f aca="false">AVERAGE(B10,C10)</f>
         <v>225000</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B11" s="9" t="n">
         <f aca="false">SUM(B2:B10)</f>
         <v>1900000</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <f aca="false">SUM(C2:C10)</f>
         <v>4300000</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <f aca="false">SUM(D2:D10)</f>
         <v>3100000</v>
       </c>
@@ -3714,170 +3815,170 @@
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>90000</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>130000</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <f aca="false">AVERAGE(F2,G2)</f>
         <v>110000</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="6" t="n">
         <f aca="false">H2*I2</f>
         <v>27500</v>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="K2" s="6" t="n">
         <f aca="false">H2+J2</f>
         <v>137500</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>45000</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>65000</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <f aca="false">AVERAGE(F3,G3)</f>
         <v>55000</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="6" t="n">
         <f aca="false">H3*I3</f>
         <v>13750</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="6" t="n">
         <f aca="false">H3+J3</f>
         <v>68750</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>110000</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <f aca="false">AVERAGE(F4,G4)</f>
         <v>130000</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="7" t="n">
         <v>0.25</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <f aca="false">H4*I4</f>
         <v>32500</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="6" t="n">
         <f aca="false">H4+J4</f>
         <v>162500</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="10" t="n">
         <f aca="false">SUM(K2:K4)</f>
         <v>368750</v>
       </c>
@@ -3902,631 +4003,631 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>275000</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <f aca="false">AVERAGE(E2,F2)</f>
         <v>637500</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>25000</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <f aca="false">AVERAGE(E3,F3)</f>
         <v>62500</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <f aca="false">AVERAGE(E4,F4)</f>
         <v>300000</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <f aca="false">AVERAGE(E5,F5)</f>
         <v>350000</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>250000</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>750000</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <f aca="false">AVERAGE(E6,F6)</f>
         <v>500000</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <f aca="false">AVERAGE(E7,F7)</f>
         <v>100000</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <f aca="false">AVERAGE(E8,F8)</f>
         <v>200000</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <f aca="false">AVERAGE(E9,F9)</f>
         <v>350000</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>120000</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>360000</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <f aca="false">AVERAGE(E10,F10)</f>
         <v>240000</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>250000</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <f aca="false">AVERAGE(E11,F11)</f>
         <v>175000</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <f aca="false">AVERAGE(E12,F12)</f>
         <v>350000</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="6" t="n">
         <f aca="false">AVERAGE(E13,F13)</f>
         <v>200000</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="6" t="n">
         <f aca="false">AVERAGE(E14,F14)</f>
         <v>350000</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>750000</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <f aca="false">AVERAGE(E15,F15)</f>
         <v>525000</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="6" t="n">
         <f aca="false">AVERAGE(E16,F16)</f>
         <v>100000</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="4" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>300000</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <f aca="false">AVERAGE(E17,F17)</f>
         <v>200000</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="4" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="5" t="n">
         <v>100000</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="5" t="n">
         <v>250000</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="6" t="n">
         <f aca="false">AVERAGE(E18,F18)</f>
         <v>175000</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="4" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>400000</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <f aca="false">AVERAGE(E19,F19)</f>
         <v>275000</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>150000</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="6" t="n">
         <f aca="false">AVERAGE(E20,F20)</f>
         <v>100000</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="4" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="9" t="n">
         <f aca="false">SUM(E2:E20)</f>
         <v>2670000</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="9" t="n">
         <f aca="false">SUM(F2:F20)</f>
         <v>7710000</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G21" s="9" t="n">
         <f aca="false">SUM(G2:G20)</f>
         <v>5190000</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="9" t="n">
         <f aca="false">SUM(H2:H20)</f>
         <v>0</v>
       </c>
@@ -4551,177 +4652,177 @@
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>500000</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>2000000</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <f aca="false">AVERAGE(E2,F2)</f>
         <v>1250000</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>250000</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <f aca="false">AVERAGE(E3,F3)</f>
         <v>625000</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>50000</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>200000</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <f aca="false">AVERAGE(E4,F4)</f>
         <v>125000</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <f aca="false">AVERAGE(E5,F5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="10" t="n">
         <f aca="false">SUM(E2:E5)</f>
         <v>800000</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="10" t="n">
         <f aca="false">SUM(F2:F5)</f>
         <v>3200000</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="10" t="n">
         <f aca="false">SUM(G2:G5)</f>
         <v>2000000</v>
       </c>
@@ -4740,217 +4841,447 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <tabColor rgb="FFCC3333"/>
+    <tabColor rgb="FF1A1A2E"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="C4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B3" s="5" t="n">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <f aca="false">'PBC Personnel'!L57</f>
         <v>5257000</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">'PBC Personnel'!M57</f>
         <v>7273000</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D6" s="14" t="n">
         <f aca="false">'PBC Personnel'!N57</f>
         <v>7831250</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="5" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="14" t="n">
         <f aca="false">'PBC Operations'!B11</f>
         <v>1900000</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">'PBC Operations'!C11</f>
         <v>4300000</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D7" s="14" t="n">
         <f aca="false">'PBC Operations'!D11</f>
         <v>3100000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="9" t="n">
+        <f aca="false">B6+B7</f>
+        <v>7157000</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <f aca="false">C6+C7</f>
+        <v>11573000</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <f aca="false">D6+D7</f>
+        <v>10931250</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <f aca="false">SUM('PBC Revenue'!E5:E20)</f>
+        <v>2270000</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <f aca="false">SUM('PBC Revenue'!F5:F20)</f>
+        <v>6110000</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <f aca="false">SUM('PBC Revenue'!G5:G20)</f>
+        <v>4190000</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <f aca="false">SUM('PBC Revenue'!E2:E4)</f>
+        <v>400000</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <f aca="false">SUM('PBC Revenue'!F2:F4)</f>
+        <v>1600000</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <f aca="false">SUM('PBC Revenue'!G2:G4)</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <f aca="false">B11+B12+B13</f>
+        <v>2670000</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <f aca="false">C11+C12+C13</f>
+        <v>7710000</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <f aca="false">D11+D12+D13</f>
+        <v>5190000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <f aca="false">B14-B8</f>
+        <v>-4487000</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <f aca="false">C14-C8</f>
+        <v>-3863000</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <f aca="false">D14-D8</f>
+        <v>-5741250</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" s="9" t="n">
+        <f aca="false">B18-D14</f>
+        <v>-5190000</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF339933"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="14" t="n">
         <f aca="false">'Nonprofit Personnel'!K5</f>
         <v>368750</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C6" s="14" t="n">
         <f aca="false">'Nonprofit Personnel'!K5</f>
         <v>368750</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D6" s="14" t="n">
         <f aca="false">'Nonprofit Personnel'!K5</f>
         <v>368750</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="8" t="n">
-        <f aca="false">B3+B4+B5</f>
-        <v>7525750</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <f aca="false">C3+C4+C5</f>
-        <v>11941750</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <f aca="false">D3+D4+D5</f>
-        <v>11300000</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <f aca="false">AVERAGE(B7,C7)</f>
+        <v>37500</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="9" t="n">
+        <f aca="false">B6+B7+B8</f>
+        <v>393750</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <f aca="false">C6+C7+C8</f>
+        <v>418750</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <f aca="false">D6+D7+D8</f>
+        <v>406250</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <f aca="false">'PBC Revenue'!E21</f>
-        <v>2670000</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <f aca="false">'PBC Revenue'!F21</f>
-        <v>7710000</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <f aca="false">'PBC Revenue'!G21</f>
-        <v>5190000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <f aca="false">'Nonprofit Revenue'!E6</f>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!E2</f>
+        <v>500000</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!F2</f>
+        <v>2000000</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!G2</f>
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!E3</f>
+        <v>250000</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!F3</f>
+        <v>1000000</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!G3</f>
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!E4</f>
+        <v>50000</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!F4</f>
+        <v>200000</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!G4</f>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <f aca="false">'Nonprofit Revenue'!G5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16" s="9" t="n">
+        <f aca="false">B12+B13+B14+B15</f>
         <v>800000</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <f aca="false">'Nonprofit Revenue'!F6</f>
+      <c r="C16" s="9" t="n">
+        <f aca="false">C12+C13+C14+C15</f>
         <v>3200000</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <f aca="false">'Nonprofit Revenue'!G6</f>
+      <c r="D16" s="9" t="n">
+        <f aca="false">D12+D13+D14+D15</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="B11" s="8" t="n">
-        <f aca="false">B9+B10</f>
-        <v>3470000</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <f aca="false">C9+C10</f>
-        <v>10910000</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <f aca="false">D9+D10</f>
-        <v>7190000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <f aca="false">B11-B6</f>
-        <v>-4055750</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <f aca="false">C11-C6</f>
-        <v>-1031750</v>
-      </c>
-      <c r="D13" s="8" t="n">
-        <f aca="false">D11-D6</f>
-        <v>-4110000</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="11" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8" t="n">
-        <f aca="false">D14-D11</f>
-        <v>-7190000</v>
+      <c r="B18" s="9" t="n">
+        <f aca="false">B16-B9</f>
+        <v>406250</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <f aca="false">C16-C9</f>
+        <v>2781250</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <f aca="false">D16-D9</f>
+        <v>1593750</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
